--- a/Test.xlsx
+++ b/Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\support2\Users\Malay\Discovery Scan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB903DD-27AF-4F31-A3BA-0D971BBEA88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6876CEFE-F4CA-4BAE-BC51-AC052995F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="1740" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="2" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>External Link</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>CIMCON LLC --- Address: http://www.EUCInsight.com\</t>
+  </si>
+  <si>
+    <t>TEst2408</t>
   </si>
 </sst>
 </file>
@@ -1343,12 +1346,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9553841-8D98-4A29-94F5-DCC5E37C4AE6}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="H9"/>
+  <dimension ref="H9:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H9" s="2" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="J16">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <v>2408</v>
       </c>
     </row>
   </sheetData>

--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\support2\Users\Malay\Discovery Scan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6876CEFE-F4CA-4BAE-BC51-AC052995F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96B7C88-49FE-4A45-BD58-7C01E9410778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
   <si>
     <t>External Link</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>TEst2408</t>
+  </si>
+  <si>
+    <t>dfgjdtyujdtyjdgfhj</t>
+  </si>
+  <si>
+    <t>tyujftyfty</t>
   </si>
 </sst>
 </file>
@@ -1346,27 +1352,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9553841-8D98-4A29-94F5-DCC5E37C4AE6}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="H9:J17"/>
+  <dimension ref="H9:N17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:14" x14ac:dyDescent="0.25">
       <c r="H9" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="8:14" x14ac:dyDescent="0.25">
+      <c r="N14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="8:14" x14ac:dyDescent="0.25">
       <c r="J15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="8:14" x14ac:dyDescent="0.25">
       <c r="J16">
         <v>2408</v>
       </c>
     </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="10:14" x14ac:dyDescent="0.25">
       <c r="J17">
         <v>2408</v>
+      </c>
+      <c r="N17" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
